--- a/demo-StatsPAI-skill/tables/table2b_iv_triplet.xlsx
+++ b/demo-StatsPAI-skill/tables/table2b_iv_triplet.xlsx
@@ -53,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -62,7 +62,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,17 +93,23 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -465,154 +494,156 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>(1) First stage</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(2) Reduced form</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>(3) 2SLS</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>(1) First stage</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>(2) Reduced form</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>(3) 2SLS</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Near 4-yr college</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>0.320***</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>0.042**</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Near 4-yr college</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>0.320***</t>
+          <t>(0.085)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>0.042**</t>
+          <t>(0.018)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>(0.085)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>(0.018)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Years of schooling</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>0.132**</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Years of schooling</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>0.132**</t>
+          <t>(0.054)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>First-stage F</t>
+        </is>
+      </c>
       <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>(0.054)</t>
+          <t>13.26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>First-stage F</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>3,010</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>3,010</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>13.26</t>
+          <t>3,010</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>3,010</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>3,010</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>3,010</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>0.195</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>0.238</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>0.477</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>0.195</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>0.238</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Standard errors in parentheses</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Standard errors in parentheses</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>* p&lt;0.10, ** p&lt;0.05, *** p&lt;0.01</t>
+          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>